--- a/test-cases/user-profile/android-user-profile-avatar-ocr-test-cases.xlsx
+++ b/test-cases/user-profile/android-user-profile-avatar-ocr-test-cases.xlsx
@@ -11,7 +11,7 @@
     <sheet name="android-profile-avatar-ocr" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'android-profile-avatar-ocr'!$A$1:$L$10</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'android-profile-avatar-ocr'!$A$1:$H$10</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,23 +23,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="65">
   <si>
     <t xml:space="preserve">Test Case ID</t>
   </si>
   <si>
-    <t xml:space="preserve">Feature Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Function</t>
-  </si>
-  <si>
     <t xml:space="preserve">Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions</t>
-  </si>
-  <si>
     <t xml:space="preserve">Test Data ID</t>
   </si>
   <si>
@@ -58,22 +49,10 @@
     <t xml:space="preserve">Evidence</t>
   </si>
   <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
     <t xml:space="preserve">TC-080</t>
   </si>
   <si>
-    <t xml:space="preserve">Android User Profile, Avatar and Student Card OCR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Profile update</t>
-  </si>
-  <si>
     <t xml:space="preserve">Update the display name and biography using valid values.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logged in as the prepared active user; the Profile screen is available.</t>
   </si>
   <si>
     <t xml:space="preserve">TD_ANDROID_PROFILE_ACCOUNT_001; TD_ANDROID_PROFILE_VALID_UPDATE_001</t>
@@ -95,19 +74,10 @@
     <t xml:space="preserve">reports/evidence/TC-080-update-profile-valid.png</t>
   </si>
   <si>
-    <t xml:space="preserve">Restore the original values after evidence is recorded if desired.</t>
-  </si>
-  <si>
     <t xml:space="preserve">TC-081</t>
   </si>
   <si>
-    <t xml:space="preserve">Profile validation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reject a username containing whitespace.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logged in as the prepared active user; Personal information is open; record the current username.</t>
   </si>
   <si>
     <t xml:space="preserve">TD_ANDROID_PROFILE_ACCOUNT_001; TD_ANDROID_PROFILE_INVALID_USERNAME_SPACE_001</t>
@@ -126,13 +96,7 @@
     <t xml:space="preserve">TC-082</t>
   </si>
   <si>
-    <t xml:space="preserve">Avatar upload</t>
-  </si>
-  <si>
     <t xml:space="preserve">Upload a valid JPEG avatar from the Android image library.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logged in as the prepared user; copy the prepared image to the device gallery; media permission is granted.</t>
   </si>
   <si>
     <t xml:space="preserve">TD_ANDROID_PROFILE_ACCOUNT_001; TD_ANDROID_AVATAR_VALID_JPEG_001</t>
@@ -151,19 +115,10 @@
     <t xml:space="preserve">NOT_RUN</t>
   </si>
   <si>
-    <t xml:space="preserve">Same as TC-080</t>
-  </si>
-  <si>
     <t xml:space="preserve">TC-083</t>
   </si>
   <si>
-    <t xml:space="preserve">Avatar size validation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reject an avatar whose processed upload remains larger than 30 MiB.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logged in as the prepared user; record the current avatar; copy the boundary image to the device gallery.</t>
   </si>
   <si>
     <t xml:space="preserve">TD_ANDROID_PROFILE_ACCOUNT_001; TD_ANDROID_AVATAR_OVER_30MB_001</t>
@@ -187,19 +142,10 @@
     <t xml:space="preserve">reports/evidence/TC-083-avt-larger-than-limit.png</t>
   </si>
   <si>
-    <t xml:space="preserve">Android image editing may reduce the selected file size; confirm the processed asset remains over the limit.</t>
-  </si>
-  <si>
     <t xml:space="preserve">TC-084</t>
   </si>
   <si>
-    <t xml:space="preserve">Avatar selection</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cancel avatar selection without changing the current avatar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logged in as the prepared user; record the current avatar.</t>
   </si>
   <si>
     <t xml:space="preserve">TD_ANDROID_PROFILE_ACCOUNT_001; TD_ANDROID_AVATAR_PICKER_CANCEL_001</t>
@@ -219,13 +165,7 @@
     <t xml:space="preserve">TC-085</t>
   </si>
   <si>
-    <t xml:space="preserve">Student Card OCR</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rescan the valid student card already owned by the same account.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The prepared account owns student ID B2400000; copy the valid card image to the device gallery; media permission is granted.</t>
   </si>
   <si>
     <t xml:space="preserve">TD_ANDROID_PROFILE_ACCOUNT_001; TD_ANDROID_OCR_VALID_OWN_CARD_001</t>
@@ -244,19 +184,10 @@
     <t xml:space="preserve">reports/evidence/TC-085-duplicate-error-free.png</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify account ownership of B2400000 before execution.</t>
-  </si>
-  <si>
     <t xml:space="preserve">TC-086</t>
   </si>
   <si>
-    <t xml:space="preserve">Student Card OCR validation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reject a student card whose student ID belongs to another user.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The prepared account is logged in; B2203551 belongs to another user; record the current verified profile values.</t>
   </si>
   <si>
     <t xml:space="preserve">TD_ANDROID_PROFILE_ACCOUNT_001; TD_ANDROID_OCR_DUPLICATE_STUDENT_ID_001</t>
@@ -280,9 +211,6 @@
     <t xml:space="preserve">Reject an image that is not a valid student card.</t>
   </si>
   <si>
-    <t xml:space="preserve">The prepared account is logged in; record the current student ID and verification state.</t>
-  </si>
-  <si>
     <t xml:space="preserve">TD_ANDROID_PROFILE_ACCOUNT_001; TD_ANDROID_OCR_NOT_STUDENT_CARD_001</t>
   </si>
   <si>
@@ -301,13 +229,7 @@
     <t xml:space="preserve">TC-089</t>
   </si>
   <si>
-    <t xml:space="preserve">Student Card OCR permission</t>
-  </si>
-  <si>
     <t xml:space="preserve">Handle denial of Android camera permission when starting student-card capture.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The prepared account is logged in; camera permission is denied or reset in Android App info.</t>
   </si>
   <si>
     <t xml:space="preserve">TD_ANDROID_PROFILE_ACCOUNT_001; TD_ANDROID_OCR_CAMERA_PERMISSION_DENIED_001</t>
@@ -322,9 +244,6 @@
   </si>
   <si>
     <t xml:space="preserve">reports/evidence/TC-089-camera-permission-denied.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reset camera permission before execution if it was previously granted permanently.</t>
   </si>
 </sst>
 </file>
@@ -334,7 +253,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -356,6 +275,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -400,16 +326,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -623,21 +553,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L1048576"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="43.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="69.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="106.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="82.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="159.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="127.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="49.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="90.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="69.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="82.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="159.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="127.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="49.15"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="2" width="10.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -665,346 +592,237 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="0" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="G3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="0" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="D4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="0" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="0" t="s">
+      <c r="H6" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="L4" s="0" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="0" t="s">
+      <c r="H7" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="J5" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="K5" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="L5" s="0" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="0" t="s">
+      <c r="H8" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="J6" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="0" t="s">
+      <c r="H9" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="10" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="H10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H7" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="I7" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="J7" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="L7" s="0" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H8" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="I8" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="J8" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="K8" s="0" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H9" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="I9" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="J9" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="0" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="F10" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H10" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="I10" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="J10" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="K10" s="0" t="s">
-        <v>90</v>
-      </c>
-      <c r="L10" s="0" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L10"/>
+  <autoFilter ref="A1:H10"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
